--- a/bom/BOM_Three_Phase_Driver_VER2.2 закупочный лист.xlsx
+++ b/bom/BOM_Three_Phase_Driver_VER2.2 закупочный лист.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EV-TECH\Desktop\Проекты\Three-Phase-80kWt\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB24A03B-9BFD-480A-9446-261DBD03A07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4538B5-29F7-4CBA-A8FE-E65526CD4CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1064,7 +1064,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" customWidth="1"/>
@@ -1075,7 +1075,7 @@
     <col min="10" max="10" width="19.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
@@ -1159,7 +1159,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
@@ -1185,7 +1185,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>17</v>
       </c>
@@ -1208,8 +1208,11 @@
         <v>135</v>
       </c>
       <c r="J5" s="14"/>
-    </row>
-    <row r="6" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
@@ -1235,7 +1238,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>20</v>
       </c>
@@ -1261,7 +1264,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
@@ -1284,8 +1287,11 @@
         <v>44</v>
       </c>
       <c r="J8" s="14"/>
-    </row>
-    <row r="9" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>24</v>
       </c>
@@ -1308,8 +1314,11 @@
         <v>7</v>
       </c>
       <c r="J9" s="14"/>
-    </row>
-    <row r="10" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>26</v>
       </c>
@@ -1332,8 +1341,11 @@
         <v>40</v>
       </c>
       <c r="J10" s="14"/>
-    </row>
-    <row r="11" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K10">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>28</v>
       </c>
@@ -1361,7 +1373,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>30</v>
       </c>
@@ -1387,7 +1399,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>31</v>
       </c>
@@ -1415,7 +1427,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>35</v>
       </c>
@@ -1440,8 +1452,11 @@
         <v>30</v>
       </c>
       <c r="J14" s="14"/>
-    </row>
-    <row r="15" spans="1:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K14">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
@@ -1467,7 +1482,7 @@
       </c>
       <c r="J15" s="14"/>
     </row>
-    <row r="16" spans="1:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>43</v>
       </c>
@@ -1493,7 +1508,7 @@
       </c>
       <c r="J16" s="14"/>
     </row>
-    <row r="17" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>47</v>
       </c>
@@ -1518,8 +1533,11 @@
         <v>15</v>
       </c>
       <c r="J17" s="14"/>
-    </row>
-    <row r="18" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>51</v>
       </c>
@@ -1544,8 +1562,11 @@
         <v>14</v>
       </c>
       <c r="J18" s="14"/>
-    </row>
-    <row r="19" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>54</v>
       </c>
@@ -1570,8 +1591,11 @@
         <v>16</v>
       </c>
       <c r="J19" s="14"/>
-    </row>
-    <row r="20" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>57</v>
       </c>
@@ -1598,8 +1622,11 @@
       <c r="J20" s="14" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>61</v>
       </c>
@@ -1624,8 +1651,11 @@
         <v>20</v>
       </c>
       <c r="J21" s="14"/>
-    </row>
-    <row r="22" spans="1:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>65</v>
       </c>
@@ -1650,8 +1680,11 @@
         <v>20</v>
       </c>
       <c r="J22" s="14"/>
-    </row>
-    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K22">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>67</v>
       </c>
@@ -1677,7 +1710,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>70</v>
       </c>
@@ -1702,8 +1735,11 @@
         <v>42</v>
       </c>
       <c r="J24" s="14"/>
-    </row>
-    <row r="25" spans="1:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K24">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>74</v>
       </c>
@@ -1727,7 +1763,7 @@
       </c>
       <c r="J25" s="14"/>
     </row>
-    <row r="26" spans="1:10" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>77</v>
       </c>
@@ -1753,7 +1789,7 @@
       </c>
       <c r="J26" s="14"/>
     </row>
-    <row r="27" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>81</v>
       </c>
@@ -1781,7 +1817,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>86</v>
       </c>
@@ -1809,7 +1845,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>90</v>
       </c>
@@ -1837,7 +1873,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>94</v>
       </c>
@@ -1865,7 +1901,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>98</v>
       </c>
@@ -1890,8 +1926,11 @@
         <v>135</v>
       </c>
       <c r="J31" s="14"/>
-    </row>
-    <row r="32" spans="1:10" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>102</v>
       </c>
@@ -1914,8 +1953,11 @@
         <v>135</v>
       </c>
       <c r="J32" s="14"/>
-    </row>
-    <row r="33" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K32">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>104</v>
       </c>
@@ -1938,8 +1980,11 @@
         <v>135</v>
       </c>
       <c r="J33" s="14"/>
-    </row>
-    <row r="34" spans="1:10" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K33">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>105</v>
       </c>
@@ -1962,8 +2007,11 @@
         <v>164</v>
       </c>
       <c r="J34" s="14"/>
-    </row>
-    <row r="35" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K34">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>107</v>
       </c>
@@ -1989,7 +2037,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>109</v>
       </c>
@@ -2012,8 +2060,11 @@
         <v>135</v>
       </c>
       <c r="J36" s="14"/>
-    </row>
-    <row r="37" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K36">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>111</v>
       </c>
@@ -2036,8 +2087,11 @@
         <v>135</v>
       </c>
       <c r="J37" s="14"/>
-    </row>
-    <row r="38" spans="1:10" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K37">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>113</v>
       </c>
@@ -2060,8 +2114,11 @@
         <v>135</v>
       </c>
       <c r="J38" s="14"/>
-    </row>
-    <row r="39" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K38">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>115</v>
       </c>
@@ -2084,8 +2141,11 @@
         <v>135</v>
       </c>
       <c r="J39" s="14"/>
-    </row>
-    <row r="40" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>117</v>
       </c>
@@ -2108,8 +2168,11 @@
         <v>135</v>
       </c>
       <c r="J40" s="14"/>
-    </row>
-    <row r="41" spans="1:10" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K40">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>119</v>
       </c>
@@ -2132,8 +2195,11 @@
         <v>135</v>
       </c>
       <c r="J41" s="14"/>
-    </row>
-    <row r="42" spans="1:10" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K41">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>121</v>
       </c>
@@ -2156,8 +2222,11 @@
         <v>135</v>
       </c>
       <c r="J42" s="14"/>
-    </row>
-    <row r="43" spans="1:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K42">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>122</v>
       </c>
@@ -2182,8 +2251,11 @@
         <v>2</v>
       </c>
       <c r="J43" s="14"/>
-    </row>
-    <row r="44" spans="1:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>125</v>
       </c>
@@ -2210,8 +2282,11 @@
       <c r="J44" s="14" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>129</v>
       </c>
@@ -2238,6 +2313,9 @@
         <v>6</v>
       </c>
       <c r="J45" s="14"/>
+      <c r="K45">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
